--- a/histograms/histogram_Nitrogen.xlsx
+++ b/histograms/histogram_Nitrogen.xlsx
@@ -445,7 +445,7 @@
         <v>0.025</v>
       </c>
       <c r="B2" t="n">
-        <v>25207</v>
+        <v>717</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>0.9750000000000001</v>
       </c>
       <c r="B21" t="n">
-        <v>1194</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
